--- a/구성종목(PDF)TIME신재생에너지액티브_2026-03-24.xlsx
+++ b/구성종목(PDF)TIME신재생에너지액티브_2026-03-24.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="75">
   <si>
     <t>종목코드</t>
   </si>
@@ -30,6 +30,216 @@
   </si>
   <si>
     <t>비중(%)</t>
+  </si>
+  <si>
+    <t>005930</t>
+  </si>
+  <si>
+    <t>삼성전자</t>
+  </si>
+  <si>
+    <t>1,218</t>
+  </si>
+  <si>
+    <t>231,054,600</t>
+  </si>
+  <si>
+    <t>009830</t>
+  </si>
+  <si>
+    <t>한화솔루션</t>
+  </si>
+  <si>
+    <t>5,100</t>
+  </si>
+  <si>
+    <t>229,500,000</t>
+  </si>
+  <si>
+    <t>000660</t>
+  </si>
+  <si>
+    <t>SK하이닉스</t>
+  </si>
+  <si>
+    <t>202,130,000</t>
+  </si>
+  <si>
+    <t>005380</t>
+  </si>
+  <si>
+    <t>현대차</t>
+  </si>
+  <si>
+    <t>172,200,000</t>
+  </si>
+  <si>
+    <t>083650</t>
+  </si>
+  <si>
+    <t>비에이치아이</t>
+  </si>
+  <si>
+    <t>1,702</t>
+  </si>
+  <si>
+    <t>168,838,400</t>
+  </si>
+  <si>
+    <t>006400</t>
+  </si>
+  <si>
+    <t>삼성SDI</t>
+  </si>
+  <si>
+    <t>167,347,500</t>
+  </si>
+  <si>
+    <t>010120</t>
+  </si>
+  <si>
+    <t>LS ELECTRIC</t>
+  </si>
+  <si>
+    <t>130,080,000</t>
+  </si>
+  <si>
+    <t>비나텍</t>
+  </si>
+  <si>
+    <t>1,028</t>
+  </si>
+  <si>
+    <t>125,930,000</t>
+  </si>
+  <si>
+    <t>000880</t>
+  </si>
+  <si>
+    <t>한화</t>
+  </si>
+  <si>
+    <t>108,755,400</t>
+  </si>
+  <si>
+    <t>000270</t>
+  </si>
+  <si>
+    <t>기아</t>
+  </si>
+  <si>
+    <t>94,740,000</t>
+  </si>
+  <si>
+    <t>062040</t>
+  </si>
+  <si>
+    <t>산일전기</t>
+  </si>
+  <si>
+    <t>91,680,000</t>
+  </si>
+  <si>
+    <t>005290</t>
+  </si>
+  <si>
+    <t>동진쎄미켐</t>
+  </si>
+  <si>
+    <t>1,500</t>
+  </si>
+  <si>
+    <t>72,300,000</t>
+  </si>
+  <si>
+    <t>HD현대중공업</t>
+  </si>
+  <si>
+    <t>70,692,000</t>
+  </si>
+  <si>
+    <t>에코프로머티</t>
+  </si>
+  <si>
+    <t>1,001</t>
+  </si>
+  <si>
+    <t>68,068,000</t>
+  </si>
+  <si>
+    <t>012330</t>
+  </si>
+  <si>
+    <t>현대모비스</t>
+  </si>
+  <si>
+    <t>66,725,000</t>
+  </si>
+  <si>
+    <t>010130</t>
+  </si>
+  <si>
+    <t>고려아연</t>
+  </si>
+  <si>
+    <t>61,720,000</t>
+  </si>
+  <si>
+    <t>원익IPS</t>
+  </si>
+  <si>
+    <t>59,268,000</t>
+  </si>
+  <si>
+    <t>078600</t>
+  </si>
+  <si>
+    <t>대주전자재료</t>
+  </si>
+  <si>
+    <t>50,783,000</t>
+  </si>
+  <si>
+    <t>씨에스윈드</t>
+  </si>
+  <si>
+    <t>50,348,000</t>
+  </si>
+  <si>
+    <t>028260</t>
+  </si>
+  <si>
+    <t>삼성물산</t>
+  </si>
+  <si>
+    <t>33,780,000</t>
+  </si>
+  <si>
+    <t>현금</t>
+  </si>
+  <si>
+    <t>32,300,104</t>
+  </si>
+  <si>
+    <t>005490</t>
+  </si>
+  <si>
+    <t>POSCO홀딩스</t>
+  </si>
+  <si>
+    <t>31,234,000</t>
+  </si>
+  <si>
+    <t>레이크머티리얼즈</t>
+  </si>
+  <si>
+    <t>19,279,260</t>
+  </si>
+  <si>
+    <t>엔켐</t>
+  </si>
+  <si>
+    <t>17,490,800</t>
   </si>
 </sst>
 </file>
@@ -98,9 +308,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
   </cellXfs>
@@ -402,7 +615,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="true" style="0"/>
@@ -429,6 +642,412 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2" spans="1:5" customHeight="1" ht="30">
+      <c r="A2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="2">
+        <v>9.81</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" customHeight="1" ht="30">
+      <c r="A3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="2">
+        <v>9.74</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" customHeight="1" ht="30">
+      <c r="A4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="2">
+        <v>205</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="2">
+        <v>8.58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" customHeight="1" ht="30">
+      <c r="A5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="2">
+        <v>350</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="2">
+        <v>7.31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" customHeight="1" ht="30">
+      <c r="A6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="2">
+        <v>7.17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" customHeight="1" ht="30">
+      <c r="A7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="2">
+        <v>421</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="2">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" customHeight="1" ht="30">
+      <c r="A8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="2">
+        <v>160</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" s="2">
+        <v>5.52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" customHeight="1" ht="30">
+      <c r="A9" s="2">
+        <v>126340</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="2">
+        <v>5.35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" customHeight="1" ht="30">
+      <c r="A10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="2">
+        <v>949</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" s="2">
+        <v>4.62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" customHeight="1" ht="30">
+      <c r="A11" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="2">
+        <v>600</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" s="2">
+        <v>4.02</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" customHeight="1" ht="30">
+      <c r="A12" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="2">
+        <v>600</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" s="2">
+        <v>3.89</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" customHeight="1" ht="30">
+      <c r="A13" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13" s="2">
+        <v>3.07</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" customHeight="1" ht="30">
+      <c r="A14" s="2">
+        <v>329180</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" s="2">
+        <v>137</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E14" s="2">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" customHeight="1" ht="30">
+      <c r="A15" s="2">
+        <v>450080</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E15" s="2">
+        <v>2.89</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" customHeight="1" ht="30">
+      <c r="A16" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="2">
+        <v>170</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E16" s="2">
+        <v>2.83</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" customHeight="1" ht="30">
+      <c r="A17" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C17" s="2">
+        <v>40</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E17" s="2">
+        <v>2.62</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" customHeight="1" ht="30">
+      <c r="A18" s="2">
+        <v>240810</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" s="2">
+        <v>440</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E18" s="2">
+        <v>2.52</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" customHeight="1" ht="30">
+      <c r="A19" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19" s="2">
+        <v>430</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E19" s="2">
+        <v>2.16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" customHeight="1" ht="30">
+      <c r="A20" s="2">
+        <v>112610</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" s="2">
+        <v>820</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E20" s="2">
+        <v>2.14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" customHeight="1" ht="30">
+      <c r="A21" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C21" s="2">
+        <v>120</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E21" s="2">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" customHeight="1" ht="30">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E22" s="2">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" customHeight="1" ht="30">
+      <c r="A23" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C23" s="2">
+        <v>92</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E23" s="2">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" customHeight="1" ht="30">
+      <c r="A24" s="2">
+        <v>281740</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E24" s="2">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" customHeight="1" ht="30">
+      <c r="A25" s="2">
+        <v>348370</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C25" s="2">
+        <v>584</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E25" s="2">
+        <v>0.74</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
